--- a/Excel/Vertical/perbandingan_Jumlah Open.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Open.xlsx
@@ -450,10 +450,10 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -473,10 +473,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>0.7368421052631579</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -496,10 +496,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>0.8734939759036144</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -519,10 +519,10 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>0.941952506596306</v>
+        <v>0.9630606860158312</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -542,10 +542,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -565,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>0.6825396825396826</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -588,10 +588,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>0.88125</v>
+        <v>0.93125</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -611,10 +611,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>0.9502762430939227</v>
+        <v>0.9668508287292817</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -634,10 +634,10 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>0.07692307692307693</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -657,10 +657,10 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>0.5</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -680,10 +680,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>0.8387096774193549</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -703,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>0.924812030075188</v>
+        <v>0.9398496240601504</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -726,10 +726,10 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>0.4705882352941176</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -749,10 +749,10 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>0.7894736842105263</v>
+        <v>0.8508771929824561</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -772,10 +772,10 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F16">
-        <v>0.9318181818181818</v>
+        <v>0.9517045454545454</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -795,10 +795,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>0.9702176403207331</v>
+        <v>0.9805269186712485</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -818,10 +818,10 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>0.8356164383561644</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -841,10 +841,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>0.9325396825396826</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -864,10 +864,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>0.9688581314878892</v>
+        <v>0.9844290657439446</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -887,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>0.9859484777517564</v>
+        <v>0.9929742388758782</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>

--- a/Excel/Vertical/perbandingan_Jumlah Open.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Open.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="15">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Turun</t>
+  </si>
+  <si>
+    <t>Naik</t>
   </si>
 </sst>
 </file>
@@ -449,6 +455,12 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -466,6 +478,12 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>76</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -483,6 +501,12 @@
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>166</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -500,6 +524,12 @@
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>379</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -517,8 +547,14 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>-0.6</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -534,8 +570,14 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>103</v>
+      </c>
+      <c r="F7">
+        <v>-0.6349206349206349</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -551,8 +593,14 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>264</v>
+      </c>
+      <c r="F8">
+        <v>-0.65</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -568,8 +616,14 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>643</v>
+      </c>
+      <c r="F9">
+        <v>-0.7762430939226519</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -585,8 +639,14 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>42</v>
+      </c>
+      <c r="F10">
+        <v>-2.230769230769231</v>
+      </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -602,8 +662,14 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>127</v>
+      </c>
+      <c r="F11">
+        <v>-1.886363636363636</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -619,8 +685,14 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>326</v>
+      </c>
+      <c r="F12">
+        <v>-1.629032258064516</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -636,8 +708,14 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>739</v>
+      </c>
+      <c r="F13">
+        <v>-1.778195488721805</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -653,8 +731,14 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>0.6470588235294118</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -670,8 +754,14 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>0.8771929824561403</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -687,8 +777,14 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>0.9573863636363636</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -704,8 +800,14 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>0.979381443298969</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -721,8 +823,14 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>0.589041095890411</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -738,8 +846,14 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>76</v>
+      </c>
+      <c r="F19">
+        <v>0.6984126984126984</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -755,8 +869,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>166</v>
+      </c>
+      <c r="F20">
+        <v>0.71280276816609</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -772,8 +892,14 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>379</v>
+      </c>
+      <c r="F21">
+        <v>0.7041373926619828</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Jumlah Open.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Open.xlsx
@@ -594,10 +594,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="F8">
-        <v>-0.65</v>
+        <v>-0.36875</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -617,10 +617,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>643</v>
+        <v>460</v>
       </c>
       <c r="F9">
-        <v>-0.7762430939226519</v>
+        <v>-0.2707182320441989</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
